--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -17,12 +17,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -43,14 +50,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -474,7 +484,95 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Château de Fargues</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Agro de Bazan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -487,7 +487,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Champagne Bérêche et Fils</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -495,7 +495,11 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>1</v>
@@ -512,24 +516,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Champagne Jacquesson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>1</v>
       </c>
@@ -545,12 +545,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -562,6 +562,399 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EURL Delmas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Languedoc-Roussillon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Limoux</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mas des Bressades</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Azienda Agricola Elio Altare</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Batasiolo SPA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Quarticello</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tenuta di Tavignano</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Agro de Bazan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bodegas Altos</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bodegas La Horra</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dominio de las Ánimas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -572,6 +965,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Château Petit Mayne</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -553,8 +553,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pomerol</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
@@ -570,7 +578,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EURL Delmas</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -578,16 +586,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Languedoc-Roussillon</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Limoux</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>1</v>
       </c>
@@ -603,7 +603,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,10 +611,14 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bourgogne</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -628,26 +632,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -661,26 +665,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -694,22 +698,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>EURL Delmas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Languedoc-Roussillon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Limoux</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -727,24 +731,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Marche</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>1</v>
       </c>
@@ -760,26 +756,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -793,24 +789,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>1</v>
       </c>
@@ -826,26 +814,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -859,20 +847,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
@@ -888,16 +880,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
@@ -913,16 +913,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
@@ -938,16 +946,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
@@ -955,6 +971,259 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bodegas Altos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bodegas La Horra</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominio de las Ánimas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Scacciadiavoli</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vinedos de Paganos</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -978,6 +1247,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -739,8 +739,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
@@ -756,26 +764,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -789,7 +789,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,10 +797,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -814,7 +822,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -822,16 +830,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>1</v>
       </c>
@@ -847,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -880,7 +880,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -913,7 +913,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -923,16 +923,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -946,26 +946,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -979,22 +971,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1012,22 +1004,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1045,7 +1037,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1055,10 +1047,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
@@ -1074,7 +1070,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1082,8 +1078,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
@@ -1099,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1107,10 +1111,18 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1124,7 +1136,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1132,7 +1144,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>1</v>
@@ -1149,7 +1165,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1174,24 +1190,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Niederösterreich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Kamptal</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>1</v>
       </c>
@@ -1207,12 +1215,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1224,6 +1232,64 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -1256,6 +1322,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Château Petit Mayne</t>
+          <t>Chateau De Gaure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -553,18 +553,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pomerol</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -578,7 +570,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Château Petit Mayne</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,8 +578,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pomerol</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
@@ -603,7 +603,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,14 +611,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -632,7 +628,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,16 +638,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jura</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Arbois</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -665,7 +657,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -675,16 +667,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -698,7 +690,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EURL Delmas</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -708,16 +700,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Languedoc-Roussillon</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Limoux</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -731,7 +723,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>EURL Delmas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,12 +733,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Languedoc-Roussillon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Limoux</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -764,7 +756,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -772,8 +764,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
@@ -789,26 +789,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -822,7 +814,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -830,10 +822,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -847,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -855,16 +855,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>1</v>
       </c>
@@ -880,7 +872,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,12 +882,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -913,7 +905,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -928,11 +920,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -946,7 +938,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -954,10 +946,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,16 +981,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1012,18 +1012,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Venetien</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Valpolicella</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1037,22 +1029,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1070,26 +1062,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1103,7 +1095,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1113,16 +1105,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1136,7 +1128,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1146,10 +1138,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -1165,7 +1161,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1173,10 +1169,18 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1190,7 +1194,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1198,7 +1202,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>1</v>
@@ -1215,7 +1223,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1240,24 +1248,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Niederösterreich</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Kamptal</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -1273,12 +1273,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1290,6 +1290,64 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -1324,6 +1382,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Distilleries et Domaines de Provence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -636,14 +636,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -657,7 +653,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -667,16 +663,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jura</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Arbois</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -690,7 +682,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,16 +692,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -723,7 +715,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EURL Delmas</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -733,16 +725,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Languedoc-Roussillon</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Limoux</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -756,7 +748,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>EURL Delmas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -766,12 +758,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Languedoc-Roussillon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Limoux</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -789,7 +781,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -797,8 +789,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
@@ -814,26 +814,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -847,12 +839,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -872,26 +864,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -905,7 +897,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -920,11 +912,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -938,7 +930,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -946,16 +938,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Emilia</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>1</v>
       </c>
@@ -971,7 +955,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -990,7 +974,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1004,7 +988,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1012,10 +996,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Colline Novaresi</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1029,7 +1021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1039,12 +1031,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1062,7 +1054,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1072,16 +1064,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1095,22 +1087,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1128,26 +1120,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1161,26 +1153,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1194,20 +1186,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
@@ -1223,18 +1219,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1248,7 +1252,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1256,8 +1260,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -1273,7 +1285,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1281,8 +1293,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bierzo</t>
+        </is>
+      </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
@@ -1298,22 +1318,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Niederösterreich</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kamptal</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1331,23 +1351,255 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominio de las Ánimas</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Terroir al Limit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vinedos de Paganos</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hofgut Falkenstein</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -1384,6 +1636,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -487,20 +487,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Champagne Bérêche et Fils</t>
+          <t>Montes S.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Champagne</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Valle Central</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Rapel</t>
+        </is>
+      </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
@@ -516,7 +520,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Champagne Jacquesson</t>
+          <t>Champagne Bérêche et Fils</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,7 +549,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chateau De Gaure</t>
+          <t>Champagne Jacquesson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -553,10 +557,14 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -570,7 +578,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Château Petit Mayne</t>
+          <t>Chateau De Gaure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -578,18 +586,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pomerol</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -603,7 +603,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Château Petit Mayne</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -611,8 +611,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pomerol</t>
+        </is>
+      </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
@@ -628,7 +636,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Distilleries et Domaines de Provence</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +661,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Distilleries et Domaines de Provence</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -661,14 +669,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -682,7 +686,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Daniel Bouland</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -692,12 +696,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jura</t>
+          <t>Bourgogne</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arbois</t>
+          <t>Beaujolais</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -715,7 +719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -725,16 +729,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Crozes-Hermitage</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -748,7 +748,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EURL Delmas</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Languedoc-Roussillon</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Limoux</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -781,7 +781,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -814,7 +814,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -822,8 +822,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Anjou-Saumur</t>
+        </is>
+      </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
@@ -839,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -847,10 +855,18 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rhonedalen</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Crozes-Hermitage</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -864,7 +880,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>EURL Delmas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,16 +890,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Provence</t>
+          <t>Languedoc-Roussillon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VdP du Var</t>
+          <t>Limoux</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -897,26 +913,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Muscadet</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -930,12 +946,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -955,24 +971,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>1</v>
       </c>
@@ -988,26 +996,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1021,7 +1029,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1031,12 +1039,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1054,7 +1062,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1069,11 +1077,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1087,7 +1095,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1097,16 +1105,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1120,7 +1128,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1128,18 +1136,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1163,16 +1163,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1196,16 +1196,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1229,16 +1229,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1252,22 +1252,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1285,26 +1285,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1318,22 +1318,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1351,22 +1351,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1384,22 +1384,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Umbrien</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Montefalco</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1413,16 +1417,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
@@ -1438,18 +1450,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1463,24 +1483,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>1</v>
       </c>
@@ -1496,12 +1512,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Serbien</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1521,22 +1537,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Podravina</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Štajerska</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1550,22 +1570,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Niederösterreich</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kamptal</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1583,16 +1603,24 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bierzo</t>
+        </is>
+      </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
@@ -1600,6 +1628,329 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bodegas Altos</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bodegas La Horra</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dominio de las Ánimas</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Legaris</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Terroir al Limit</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Vinedos de Paganos</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hofgut Falkenstein</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -1644,6 +1995,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -880,7 +880,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EURL Delmas</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Languedoc-Roussillon</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Limoux</t>
+          <t>Muscadet</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -913,7 +913,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,16 +921,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Loiredalen</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Muscadet</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>1</v>
       </c>
@@ -946,7 +938,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -971,7 +963,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -979,10 +971,18 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Provence</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VdP du Var</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -996,26 +996,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Provence</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VdP du Var</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Colli Aprutini</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1062,7 +1062,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1077,11 +1077,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dogliani</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1103,18 +1103,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1128,7 +1120,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1136,8 +1128,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -1153,7 +1153,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1168,11 +1168,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1196,16 +1196,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1252,7 +1252,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1262,16 +1262,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1295,16 +1295,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1328,16 +1328,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1394,16 +1394,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1427,16 +1427,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1450,26 +1450,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Venetien</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Valpolicella</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1483,19 +1479,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Dão</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>1</v>
@@ -1512,16 +1504,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Serbien</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>Slovenien</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Podravina</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Štajerska</t>
+        </is>
+      </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
@@ -1537,22 +1537,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Podravina</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Štajerska</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1570,7 +1570,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Bierzo</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1603,7 +1603,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1636,7 +1636,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1646,16 +1646,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Ribera del Duero</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1679,16 +1679,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1702,7 +1698,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1710,11 +1706,7 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Navarra</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>1</v>
@@ -1731,7 +1723,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1756,7 +1748,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1764,8 +1756,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
@@ -1781,7 +1781,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Katalonien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Priorat</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1814,7 +1814,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1822,16 +1822,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>1</v>
       </c>
@@ -1847,18 +1839,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Hofgut Falkenstein</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mosel</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1872,22 +1868,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Starmont Winery &amp; Vineyards</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -487,22 +487,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Montes S.A.</t>
+          <t>Aphelion Wine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Australien</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Valle Central</t>
+          <t>South Australia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rapel</t>
+          <t>Fleurieu</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -520,20 +520,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Champagne Bérêche et Fils</t>
+          <t>Montes S.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Champagne</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Valle Central</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rapel</t>
+        </is>
+      </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
@@ -549,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Champagne Jacquesson</t>
+          <t>BWINE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,10 +563,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Champagne</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bordeaux Supérieur</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
@@ -578,7 +586,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chateau De Gaure</t>
+          <t>Champagne Bérêche et Fils</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,10 +594,14 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -603,7 +615,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Château Petit Mayne</t>
+          <t>Champagne Jacquesson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,14 +625,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pomerol</t>
-        </is>
-      </c>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>1</v>
       </c>
@@ -636,7 +644,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Chateau De Gaure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,7 +655,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -661,7 +669,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Distilleries et Domaines de Provence</t>
+          <t>Château Haut-Bages-Libéral</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -669,8 +677,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Haut-Médoc</t>
+        </is>
+      </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
@@ -686,7 +702,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Domaine Daniel Bouland</t>
+          <t>Château Petit Mayne</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -696,12 +712,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bourgogne</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Beaujolais</t>
+          <t>Pomerol</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -719,7 +735,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Château Phélan-Ségur</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,12 +745,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Haut-Médoc</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -748,7 +768,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Domaine Serre Besson</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -756,16 +776,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rhonedalen</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Vinsobres</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>1</v>
       </c>
@@ -781,7 +793,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Distilleries et Domaines de Provence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -789,16 +801,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jura</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Arbois</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>1</v>
       </c>
@@ -814,7 +818,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Domaine aux Moines</t>
+          <t>Domaine Daniel Bouland</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -824,12 +828,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Bourgogne</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Anjou-Saumur</t>
+          <t>Beaujolais</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -847,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -857,16 +861,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Crozes-Hermitage</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -880,7 +880,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -913,7 +913,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,8 +921,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jura</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Arbois</t>
+        </is>
+      </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
@@ -938,7 +946,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -946,8 +954,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Anjou-Saumur</t>
+        </is>
+      </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
@@ -963,7 +979,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -973,16 +989,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Provence</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VdP du Var</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -996,24 +1012,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>Kriter Brut de Brut</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Abruzzerna</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Colli Aprutini</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>1</v>
       </c>
@@ -1029,22 +1037,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dogliani</t>
+          <t>Muscadet</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1062,26 +1070,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1120,26 +1120,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1163,16 +1163,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1219,7 +1219,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1229,16 +1229,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1260,18 +1260,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1285,7 +1277,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1295,12 +1287,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1318,7 +1310,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1333,11 +1325,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1351,7 +1343,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1361,16 +1353,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1384,7 +1376,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1394,12 +1386,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1417,7 +1409,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1427,16 +1419,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1450,20 +1442,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dão</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Chianti Classico</t>
+        </is>
+      </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
@@ -1479,16 +1475,24 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Serbien</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
@@ -1504,26 +1508,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Podravina</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Štajerska</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1537,24 +1541,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>1</v>
       </c>
@@ -1570,26 +1566,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1603,22 +1599,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1636,22 +1632,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1669,20 +1665,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rosso di Montalcino</t>
+        </is>
+      </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
@@ -1698,18 +1698,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1723,15 +1723,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dão</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
         <v>1</v>
@@ -1748,24 +1752,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
         <v>1</v>
       </c>
@@ -1781,22 +1777,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Katalonien</t>
+          <t>Podravina</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Priorat</t>
+          <t>Štajerska</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1814,7 +1810,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1822,8 +1818,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
@@ -1839,22 +1843,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bierzo</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1868,26 +1876,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kalifornien</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1901,26 +1909,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Niederösterreich</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kamptal</t>
+          <t>Ribera del Duero</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1934,15 +1942,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>1</v>
@@ -1951,6 +1963,321 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dominio de las Ánimas</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Finca Antigua</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Legaris</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Terroir al Limit</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Vinedos de Paganos</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hofgut Falkenstein</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Six Eighty Cellars</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Starmont Winery &amp; Vineyards</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2006,6 +2333,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chateau De Gaure</t>
+          <t>Chateau Clos du Roy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,10 +652,18 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sauternes</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -669,7 +677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Château Haut-Bages-Libéral</t>
+          <t>Chateau De Gaure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,18 +685,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Haut-Médoc</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -702,7 +702,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Château Petit Mayne</t>
+          <t>Château Haut Picorneau</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -710,16 +710,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Pomerol</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>1</v>
       </c>
@@ -735,7 +727,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Château Phélan-Ségur</t>
+          <t>Château Haut-Bages-Libéral</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -768,7 +760,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Château de Fargues</t>
+          <t>Château Petit Mayne</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -776,8 +768,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pomerol</t>
+        </is>
+      </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
@@ -793,7 +793,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distilleries et Domaines de Provence</t>
+          <t>Château Phélan-Ségur</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -801,8 +801,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Haut-Médoc</t>
+        </is>
+      </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
@@ -818,7 +826,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Domaine Daniel Bouland</t>
+          <t>Château de Fargues</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -826,16 +834,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Beaujolais</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Distilleries et Domaines de Provence</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -859,14 +859,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -880,7 +876,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Domaine Serre Besson</t>
+          <t>Domaine Daniel Bouland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -890,12 +886,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Bourgogne</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vinsobres</t>
+          <t>Beaujolais</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -913,7 +909,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -923,16 +919,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jura</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Arbois</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -946,7 +938,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Domaine aux Moines</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -956,12 +948,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anjou-Saumur</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -979,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -989,16 +981,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1012,7 +1004,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kriter Brut de Brut</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1020,8 +1012,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Anjou-Saumur</t>
+        </is>
+      </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
@@ -1037,7 +1037,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1047,16 +1047,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Kriter Brut de Brut</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1103,8 +1103,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
@@ -1120,7 +1128,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1128,18 +1136,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Provence</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VdP du Var</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1153,26 +1153,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>S.C.E.A Château d'Aiguilhe Querre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Colli Aprutini</t>
-        </is>
-      </c>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1186,24 +1182,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Dogliani</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>1</v>
       </c>
@@ -1219,22 +1207,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1252,7 +1240,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1260,8 +1248,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Abruzzerna</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Colli Aprutini</t>
+        </is>
+      </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -1277,7 +1273,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,7 +1288,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1310,7 +1306,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1325,11 +1321,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1343,7 +1339,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1353,12 +1349,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1376,7 +1372,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1384,16 +1380,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Venetien</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Valpolicella</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>1</v>
       </c>
@@ -1409,7 +1397,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1428,7 +1416,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1442,7 +1430,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mori Concetta</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1452,16 +1440,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Chianti Classico</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1475,7 +1463,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1485,12 +1473,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1508,7 +1496,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1518,16 +1506,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1541,7 +1529,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Réva</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,10 +1537,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1566,7 +1562,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1576,16 +1572,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Chianti Classico</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1599,7 +1595,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Oltretorrente</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1609,16 +1605,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Colli Tortonesi</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1632,7 +1628,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1642,16 +1638,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1665,7 +1661,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Villa i Cipressi</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1675,16 +1671,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rosso di Montalcino</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1698,18 +1694,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marlobobo AS</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1723,22 +1719,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dão</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Umbrien</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Montefalco</t>
+        </is>
+      </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1752,16 +1752,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Serbien</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
@@ -1777,26 +1785,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Podravina</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Štajerska</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1810,22 +1818,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Rosso di Montalcino</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1843,26 +1851,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Bierzo</t>
-        </is>
-      </c>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1876,24 +1876,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>1</v>
       </c>
@@ -1909,26 +1905,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1942,20 +1930,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Podravina</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Štajerska</t>
+        </is>
+      </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
@@ -1971,7 +1963,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1979,8 +1971,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
@@ -1996,7 +1996,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2004,8 +2004,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bierzo</t>
+        </is>
+      </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
@@ -2021,7 +2029,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2031,12 +2039,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Galicien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Rías Baixas</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2054,7 +2062,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2064,16 +2072,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Katalonien</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Priorat</t>
+          <t>Ribera del Duero</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -2087,7 +2095,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2095,7 +2103,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
         <v>1</v>
@@ -2112,22 +2124,18 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Mosel</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2141,18 +2149,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Six Eighty Cellars</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -2166,26 +2174,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kalifornien</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Ribera del Duero</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -2199,22 +2207,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Niederösterreich</t>
+          <t>Katalonien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kamptal</t>
+          <t>Priorat</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2232,12 +2240,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2257,27 +2265,172 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Weingut Stefanie Renner</t>
+          <t>Hofgut Falkenstein</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Weinland Österreich</t>
+          <t>Mosel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Six Eighty Cellars</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Starmont Winery &amp; Vineyards</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2344,6 +2497,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Domaine Daniel Bouland</t>
+          <t>Domaine Bersan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Beaujolais</t>
+          <t>Bourgogne Aligoté</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -909,7 +909,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Domaine Daniel Bouland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -922,9 +922,13 @@
           <t>Bourgogne</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Beaujolais</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -938,7 +942,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Domaine Serre Besson</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -948,16 +952,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Vinsobres</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jura</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arbois</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1004,7 +1004,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Domaine aux Moines</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Anjou-Saumur</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1037,7 +1037,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1047,16 +1047,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Anjou-Saumur</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kriter Brut de Brut</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1078,10 +1078,18 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rhonedalen</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Crozes-Hermitage</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1095,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Kriter Brut de Brut</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1103,16 +1111,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Loiredalen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Muscadet</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>1</v>
       </c>
@@ -1128,7 +1128,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1136,8 +1136,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -1153,7 +1161,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S.C.E.A Château d'Aiguilhe Querre</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1161,14 +1169,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1182,7 +1186,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>S.C.E.A Château d'Aiguilhe Querre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1190,10 +1194,14 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1207,7 +1215,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1215,18 +1223,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Provence</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VdP du Var</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1240,26 +1240,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Colli Aprutini</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1273,24 +1273,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>Vignobles Touchais</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Dogliani</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>1</v>
       </c>
@@ -1306,7 +1298,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1316,16 +1308,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1339,7 +1331,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1349,12 +1341,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1372,7 +1364,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1380,10 +1372,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1430,7 +1430,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1438,18 +1438,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Colline Novaresi</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1463,7 +1455,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1473,12 +1465,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1496,7 +1488,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1506,16 +1498,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1529,7 +1521,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1539,16 +1531,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1562,7 +1554,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mori Concetta</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1572,12 +1564,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Chianti Classico</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1595,7 +1587,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oltretorrente</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1610,11 +1602,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Colli Tortonesi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1628,7 +1620,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1638,12 +1630,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Chianti Classico</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1661,7 +1653,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Oltretorrente</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1676,11 +1668,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Colli Tortonesi</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1694,7 +1686,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Réva</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1702,8 +1694,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
@@ -1719,7 +1719,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1760,16 +1760,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Marche</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
         <v>1</v>
       </c>
@@ -1785,7 +1777,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1795,16 +1787,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1818,7 +1810,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Villa i Cipressi</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1828,12 +1820,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rosso di Montalcino</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1851,18 +1843,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marlobobo AS</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Norge</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1876,20 +1876,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dão</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Rosso di Montalcino</t>
+        </is>
+      </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
@@ -1905,18 +1909,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Serbien</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1930,24 +1934,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Podravina</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Štajerska</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>1</v>
       </c>
@@ -1963,24 +1963,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
         <v>1</v>
       </c>
@@ -1996,22 +1988,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Podravina</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Štajerska</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2029,7 +2021,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2062,7 +2054,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2077,11 +2069,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Bierzo</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -2095,7 +2087,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2105,10 +2097,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
@@ -2124,7 +2120,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2132,10 +2128,18 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2149,7 +2153,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2157,7 +2161,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
         <v>1</v>
@@ -2174,7 +2182,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2182,16 +2190,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>1</v>
       </c>
@@ -2207,7 +2207,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2215,16 +2215,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>1</v>
       </c>
@@ -2240,7 +2232,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2248,8 +2240,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -2265,22 +2265,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -2294,18 +2298,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Six Eighty Cellars</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -2319,26 +2323,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Hofgut Falkenstein</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kalifornien</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>North Coast</t>
-        </is>
-      </c>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -2352,26 +2352,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Six Eighty Cellars</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Niederösterreich</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Kamptal</t>
-        </is>
-      </c>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2385,18 +2377,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Starmont Winery &amp; Vineyards</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Weingut Stefanie Renner</t>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2420,10 +2420,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Weinland Österreich</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
@@ -2431,6 +2435,60 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2502,6 +2560,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1298,24 +1298,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>Periani Wine LLC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Georgien</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Colli Aprutini</t>
-        </is>
-      </c>
+          <t>Kakheti</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>1</v>
       </c>
@@ -1331,7 +1327,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1341,12 +1337,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dogliani</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1364,7 +1360,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1379,11 +1375,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1397,7 +1393,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1407,16 +1403,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1430,7 +1426,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1438,8 +1434,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
@@ -1455,7 +1459,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1463,16 +1467,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>1</v>
       </c>
@@ -1488,7 +1484,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1503,11 +1499,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
@@ -1521,7 +1517,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1531,16 +1527,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1554,7 +1550,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1564,12 +1560,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1587,7 +1583,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1597,16 +1593,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1620,7 +1616,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mori Concetta</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1630,16 +1626,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chianti Classico</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1653,7 +1649,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oltretorrente</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1663,16 +1659,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Colli Tortonesi</t>
+          <t>Chianti Classico</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1686,7 +1682,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Oltretorrente</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1696,16 +1692,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Colli Tortonesi</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1719,7 +1715,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1729,16 +1725,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1752,7 +1748,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Réva</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1760,10 +1756,18 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1777,7 +1781,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1785,18 +1789,10 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Umbrien</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Montefalco</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1810,7 +1806,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1820,16 +1816,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1843,7 +1839,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1853,16 +1849,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1876,7 +1872,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Villa i Cipressi</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1886,16 +1882,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Rosso di Montalcino</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1909,18 +1905,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marlobobo AS</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Norge</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Rosso di Montalcino</t>
+        </is>
+      </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1934,19 +1938,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Heya Wines</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Dão</t>
-        </is>
-      </c>
+          <t>Libanon</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>1</v>
@@ -1963,18 +1963,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Serbien</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1988,24 +1988,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Podravina</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Štajerska</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
         <v>1</v>
       </c>
@@ -2021,24 +2017,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
         <v>1</v>
       </c>
@@ -2054,22 +2042,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Podravina</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Štajerska</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2087,7 +2075,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2120,7 +2108,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2135,11 +2123,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Bierzo</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2153,7 +2141,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2163,10 +2151,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
@@ -2182,7 +2174,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2190,10 +2182,18 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2215,7 +2215,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>1</v>
@@ -2232,7 +2236,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2240,16 +2244,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -2265,7 +2261,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2273,16 +2269,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>1</v>
       </c>
@@ -2298,7 +2286,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2306,8 +2294,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
@@ -2323,22 +2319,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -2352,18 +2352,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Six Eighty Cellars</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2377,26 +2377,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Hofgut Falkenstein</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kalifornien</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>North Coast</t>
-        </is>
-      </c>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2410,26 +2406,18 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Six Eighty Cellars</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Niederösterreich</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Kamptal</t>
-        </is>
-      </c>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -2443,18 +2431,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Starmont Winery &amp; Vineyards</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
@@ -2468,7 +2464,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Weingut Stefanie Renner</t>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2478,10 +2474,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Weinland Österreich</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
@@ -2489,6 +2489,60 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2562,6 +2616,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Domaine Serre Besson</t>
+          <t>Domaine Paul Prieur &amp; Fils</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Vinsobres</t>
+          <t>Sancerre</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1004,7 +1004,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jura</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arbois</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1037,7 +1037,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Domaine aux Moines</t>
+          <t>Domaine Vendôme</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Anjou-Saumur</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1070,7 +1070,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1080,16 +1080,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kriter Brut de Brut</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1111,8 +1111,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Anjou-Saumur</t>
+        </is>
+      </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
@@ -1128,7 +1136,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Domaine des Aubuisières</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1143,7 +1151,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Muscadet</t>
+          <t>Touraine</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1161,7 +1169,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Domaine du Bouchot</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1169,8 +1177,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pouilly Fumé</t>
+        </is>
+      </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
@@ -1186,7 +1202,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S.C.E.A Château d'Aiguilhe Querre</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1196,10 +1212,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Rhonedalen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Crozes-Hermitage</t>
+        </is>
+      </c>
       <c r="E25" t="n">
         <v>4</v>
       </c>
@@ -1215,7 +1235,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>Kriter Brut de Brut</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1240,7 +1260,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,16 +1270,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Provence</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VdP du Var</t>
+          <t>Muscadet</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1273,7 +1293,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vignobles Touchais</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1298,17 +1318,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Periani Wine LLC</t>
+          <t>Remy Massin &amp; Fils</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Georgien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kakheti</t>
+          <t>Champagne</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1327,26 +1347,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>S.C.E.A Château d'Aiguilhe Querre</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Colli Aprutini</t>
-        </is>
-      </c>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1360,24 +1376,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Italien</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Dogliani</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>1</v>
       </c>
@@ -1393,22 +1401,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1426,22 +1434,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
+          <t>Terres Blanches</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Sancerre</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1459,12 +1467,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Vignobles Touchais</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1484,24 +1492,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Periani Wine LLC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Georgien</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+          <t>Kakheti</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>1</v>
       </c>
@@ -1517,7 +1521,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1527,16 +1531,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Colline Novaresi</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1550,7 +1554,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1560,12 +1564,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1583,7 +1587,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1593,16 +1597,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1616,7 +1620,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1626,16 +1630,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1649,7 +1653,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mori Concetta</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1657,16 +1661,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Toscana</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Chianti Classico</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>1</v>
       </c>
@@ -1682,7 +1678,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oltretorrente</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1697,11 +1693,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Colli Tortonesi</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1715,7 +1711,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1725,16 +1721,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Monferrato</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1748,7 +1744,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1758,16 +1754,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1781,7 +1777,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Réva</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1789,8 +1785,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
@@ -1806,7 +1810,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1816,16 +1820,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1839,7 +1843,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1849,12 +1853,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marche</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
+          <t>Chianti Classico</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1872,7 +1876,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Oltretorrente</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1882,12 +1886,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Colli Tortonesi</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1905,7 +1909,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Villa i Cipressi</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1915,12 +1919,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Rosso di Montalcino</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1938,18 +1942,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Heya Wines</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Libanon</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Piemonte</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Barolo</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -1963,18 +1975,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marlobobo AS</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1988,22 +2000,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dão</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Umbrien</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Montefalco</t>
+        </is>
+      </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -2017,16 +2033,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Serbien</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Marche</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Verdicchio dei Castelli di Jesi</t>
+        </is>
+      </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
@@ -2042,26 +2066,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Podravina</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Štajerska</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -2075,22 +2099,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Rosso di Montalcino</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2108,24 +2132,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Heya Wines</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Bierzo</t>
-        </is>
-      </c>
+          <t>Libanon</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
         <v>1</v>
       </c>
@@ -2141,26 +2157,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -2174,26 +2182,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -2207,19 +2211,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Navarra</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>1</v>
@@ -2236,16 +2236,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>Slovenien</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Podravina</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Štajerska</t>
+        </is>
+      </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -2261,7 +2269,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2269,8 +2277,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
@@ -2286,7 +2302,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2301,7 +2317,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ribera del Duero</t>
+          <t>Bierzo</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2319,7 +2335,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>BODEGAS Y VIÑEDOS EL PACTO S.L.U.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2329,14 +2345,10 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+          <t>Rioja</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>1</v>
       </c>
@@ -2352,7 +2364,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2360,8 +2372,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
@@ -2377,22 +2397,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mosel</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2406,18 +2430,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Six Eighty Cellars</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -2431,26 +2459,18 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Kalifornien</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>North Coast</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
@@ -2464,24 +2484,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Niederösterreich</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Kamptal</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>1</v>
       </c>
@@ -2497,16 +2509,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Österrike</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
@@ -2522,20 +2542,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Weingut Stefanie Renner</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Weinland Österreich</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Katalonien</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
@@ -2543,6 +2567,238 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Vinedos de Paganos</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Simpsons Wine Estate</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Storbritannien</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Hofgut Falkenstein</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Six Eighty Cellars</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Starmont Winery &amp; Vineyards</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2618,6 +2874,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/att_googla.xlsx
+++ b/data/att_googla.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Domaine Bersan</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -886,16 +886,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bourgogne</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bourgogne Aligoté</t>
-        </is>
-      </c>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -909,7 +905,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Domaine Daniel Bouland</t>
+          <t>Domaine Bersan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -924,11 +920,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Beaujolais</t>
+          <t>Bourgogne Aligoté</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -942,7 +938,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Domaine Michel Rebourgeon</t>
+          <t>Domaine Daniel Bouland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -955,9 +951,13 @@
           <t>Bourgogne</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Beaujolais</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Domaine Paul Prieur &amp; Fils</t>
+          <t>Domaine Michel Rebourgeon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,16 +981,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Sancerre</t>
-        </is>
-      </c>
+          <t>Bourgogne</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1004,7 +1000,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Domaine Serre Besson</t>
+          <t>Domaine Paul Prieur &amp; Fils</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1014,12 +1010,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Vinsobres</t>
+          <t>Sancerre</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1037,7 +1033,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Domaine Vendôme</t>
+          <t>Domaine Serre Besson</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Vinsobres</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1070,7 +1066,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Domaine Villet</t>
+          <t>Domaine Vendôme</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1080,12 +1076,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jura</t>
+          <t>Rhonedalen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Arbois</t>
+          <t>Crozes-Hermitage</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1103,7 +1099,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Domaine aux Moines</t>
+          <t>Domaine Villet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1113,12 +1109,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Jura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Anjou-Saumur</t>
+          <t>Arbois</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1136,7 +1132,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Domaine des Aubuisières</t>
+          <t>Domaine aux Moines</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1151,7 +1147,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Touraine</t>
+          <t>Anjou-Saumur</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1169,7 +1165,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Domaine du Bouchot</t>
+          <t>Domaine des Aubuisières</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pouilly Fumé</t>
+          <t>Touraine</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1202,7 +1198,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Domaine les 4 Vents</t>
+          <t>Domaine du Bouchot</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1212,16 +1208,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rhonedalen</t>
+          <t>Loiredalen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Crozes-Hermitage</t>
+          <t>Pouilly Fumé</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1235,7 +1231,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kriter Brut de Brut</t>
+          <t>Domaine les 4 Vents</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1243,10 +1239,18 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rhonedalen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Crozes-Hermitage</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1260,7 +1264,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maison Aux Alouettes</t>
+          <t>Kriter Brut de Brut</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1268,16 +1272,8 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Loiredalen</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Muscadet</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -1293,7 +1289,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mas des Bressades</t>
+          <t>Maison Aux Alouettes</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1301,8 +1297,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Muscadet</t>
+        </is>
+      </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
@@ -1318,7 +1322,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Remy Massin &amp; Fils</t>
+          <t>Mas des Bressades</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1326,11 +1330,7 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Champagne</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>1</v>
@@ -1347,7 +1347,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S.C.E.A Château d'Aiguilhe Querre</t>
+          <t>Remy Massin &amp; Fils</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
+          <t>Champagne</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAS ICE TROPEZ</t>
+          <t>S.C.E.A Château d'Aiguilhe Querre</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1384,10 +1384,14 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1401,7 +1405,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAS TROPEZ</t>
+          <t>SAS ICE TROPEZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1409,18 +1413,10 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Provence</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VdP du Var</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1434,7 +1430,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Terres Blanches</t>
+          <t>SAS TROPEZ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1444,16 +1440,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Loiredalen</t>
+          <t>Provence</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sancerre</t>
+          <t>VdP du Var</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1467,7 +1463,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vignobles Touchais</t>
+          <t>Terres Blanches</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1475,8 +1471,16 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Loiredalen</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sancerre</t>
+        </is>
+      </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
@@ -1492,19 +1496,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Periani Wine LLC</t>
+          <t>Vignobles Touchais</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Georgien</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Kakheti</t>
-        </is>
-      </c>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>1</v>
@@ -1521,24 +1521,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Antica Cantina Pietramore</t>
+          <t>Periani Wine LLC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Georgien</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Abruzzerna</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Colli Aprutini</t>
-        </is>
-      </c>
+          <t>Kakheti</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>1</v>
       </c>
@@ -1554,7 +1550,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azienda Agricola Altare di Altare Nicholas</t>
+          <t>Antica Cantina Pietramore</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1564,12 +1560,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Abruzzerna</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Dogliani</t>
+          <t>Colli Aprutini</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1587,7 +1583,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azienda Agricola Elio Altare</t>
+          <t>Azienda Agricola Altare di Altare Nicholas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1602,11 +1598,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Dogliani</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1620,7 +1616,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
+          <t>Azienda Agricola Elio Altare</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1630,16 +1626,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1653,7 +1649,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
+          <t>Azienda Agricola Milanese Ivana di Gazzo Paolo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1661,8 +1657,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
@@ -1678,7 +1682,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Batasiolo SPA</t>
+          <t>Azienda Agricola Rabino Luigi Giuseppe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1686,16 +1690,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Piemonte</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Barolo</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>1</v>
       </c>
@@ -1711,7 +1707,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
+          <t>Batasiolo SPA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1726,11 +1722,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Monferrato</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1744,7 +1740,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Casino Nitti</t>
+          <t>Cantine Rogiotto di Minazzoli Christian &amp; C.S.a.s.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1754,16 +1750,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kampanien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Greco di Tufo</t>
+          <t>Colline Novaresi</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1777,7 +1773,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cà la Biondi</t>
+          <t>Casino Nitti</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1787,12 +1783,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Kampanien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Greco di Tufo</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1810,7 +1806,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>E. Pira &amp; Figli Chiara Boschis</t>
+          <t>Cà la Biondi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1820,16 +1816,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Venetien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Valpolicella</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1843,7 +1839,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mori Concetta</t>
+          <t>E. Pira &amp; Figli Chiara Boschis</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1853,16 +1849,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Chianti Classico</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1876,7 +1872,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Oltretorrente</t>
+          <t>Mori Concetta</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1886,16 +1882,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Colli Tortonesi</t>
+          <t>Chianti Classico</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1909,7 +1905,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quarticello</t>
+          <t>Oltretorrente</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1919,16 +1915,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Colli Tortonesi</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1942,7 +1938,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rocche Costamagna</t>
+          <t>Poderi Fogliati di Annalisa Chiappa</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1961,7 +1957,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -1975,7 +1971,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Réva</t>
+          <t>Quarticello</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1983,8 +1979,16 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
@@ -2000,7 +2004,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Scacciadiavoli</t>
+          <t>Rocche Costamagna</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2010,16 +2014,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Umbrien</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Montefalco</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -2033,7 +2037,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tenuta di Tavignano</t>
+          <t>Réva</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2041,16 +2045,8 @@
           <t>Italien</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Marche</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Verdicchio dei Castelli di Jesi</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
         <v>1</v>
       </c>
@@ -2066,7 +2062,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Villa della Torre</t>
+          <t>Scacciadiavoli</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2076,16 +2072,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Venetien</t>
+          <t>Umbrien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Valpolicella</t>
+          <t>Montefalco</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -2099,7 +2095,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Villa i Cipressi</t>
+          <t>Tenuta di Tavignano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2109,12 +2105,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Marche</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Rosso di Montalcino</t>
+          <t>Verdicchio dei Castelli di Jesi</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2132,18 +2128,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Heya Wines</t>
+          <t>Villa della Torre</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Libanon</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Venetien</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Valpolicella</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -2157,18 +2161,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marlobobo AS</t>
+          <t>Villa i Cipressi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Norge</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>Italien</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Toscana</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Rosso di Montalcino</t>
+        </is>
+      </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -2182,19 +2194,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nuno Mira do Ó</t>
+          <t>Heya Wines</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Dão</t>
-        </is>
-      </c>
+          <t>Libanon</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>1</v>
@@ -2211,18 +2219,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VINARIJA FENEK DOO</t>
+          <t>Marlobobo AS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Serbien</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -2236,24 +2244,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kobal Wine Estate D.O.O.</t>
+          <t>Nuno Mira do Ó</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Slovenien</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Podravina</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Štajerska</t>
-        </is>
-      </c>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -2269,24 +2273,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Agro de Bazan</t>
+          <t>VINARIJA FENEK DOO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spanien</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Galicien</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Rías Baixas</t>
-        </is>
-      </c>
+          <t>Serbien</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>1</v>
       </c>
@@ -2302,22 +2298,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Antoine Graillot &amp; Raul Perez</t>
+          <t>Kobal Wine Estate D.O.O.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Slovenien</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
+          <t>Podravina</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bierzo</t>
+          <t>Štajerska</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2335,7 +2331,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BODEGAS Y VIÑEDOS EL PACTO S.L.U.</t>
+          <t>Agro de Bazan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2345,10 +2341,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rioja</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
@@ -2364,7 +2364,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bodegas Altos</t>
+          <t>Antoine Graillot &amp; Raul Perez</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Galicien</t>
+          <t>Kastilien-León</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rías Baixas</t>
+          <t>Bierzo</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2397,7 +2397,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bodegas La Horra</t>
+          <t>BODEGAS Y VIÑEDOS EL PACTO S.L.U.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2407,16 +2407,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+          <t>Rioja</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2430,7 +2426,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Compañia Vitivinícola Tandem S.A.</t>
+          <t>Bodegas Altos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2440,10 +2436,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Galicien</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rías Baixas</t>
+        </is>
+      </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
@@ -2459,7 +2459,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dominio de las Ánimas</t>
+          <t>Bodegas La Horra</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2467,10 +2467,18 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
@@ -2484,7 +2492,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Finca Antigua</t>
+          <t>Compañia Vitivinícola Tandem S.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2492,7 +2500,11 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>1</v>
@@ -2509,7 +2521,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Legaris</t>
+          <t>Dominio de las Ánimas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2517,16 +2529,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Kastilien-León</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Ribera del Duero</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
         <v>1</v>
       </c>
@@ -2542,7 +2546,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Terroir al Limit</t>
+          <t>Finca Antigua</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2550,16 +2554,8 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Katalonien</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Priorat</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>1</v>
       </c>
@@ -2575,7 +2571,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vinedos de Paganos</t>
+          <t>Legaris</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2583,8 +2579,16 @@
           <t>Spanien</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Kastilien-León</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Ribera del Duero</t>
+        </is>
+      </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
@@ -2600,26 +2604,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Simpsons Wine Estate</t>
+          <t>Terroir al Limit</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Storbritannien</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Katalonien</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Priorat</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -2633,22 +2637,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hofgut Falkenstein</t>
+          <t>Vinedos de Paganos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Mosel</t>
-        </is>
-      </c>
+          <t>Spanien</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
@@ -2662,18 +2662,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Six Eighty Cellars</t>
+          <t>Simpsons Wine Estate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Storbritannien</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
@@ -2687,26 +2695,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Starmont Winery &amp; Vineyards</t>
+          <t>Hofgut Falkenstein</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kalifornien</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>North Coast</t>
-        </is>
-      </c>
+          <t>Mosel</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2720,22 +2724,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+          <t>Radio-Coteau</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Niederösterreich</t>
+          <t>Kalifornien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kamptal</t>
+          <t>North Coast</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2753,18 +2757,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JOISEPH Natur Weingut</t>
+          <t>Six Eighty Cellars</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -2778,27 +2782,118 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Weingut Stefanie Renner</t>
+          <t>Starmont Winery &amp; Vineyards</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Österrike</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Weinland Österreich</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Kalifornien</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Bergkellerei Godfried Steinschaden GmbH</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Kamptal</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JOISEPH Natur Weingut</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>Google →</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Weingut Stefanie Renner</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Österrike</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Weinland Österreich</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr">
         <is>
           <t>Google →</t>
         </is>
@@ -2882,6 +2977,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
